--- a/data/trans_dic/P2A_psíq_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,82</t>
+          <t>0,21; 1,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,01</t>
+          <t>0,48; 6,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,34</t>
+          <t>0,89; 3,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,83</t>
+          <t>0,43; 6,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,02</t>
+          <t>0,65; 1,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,42</t>
+          <t>0,17; 1,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,5</t>
+          <t>0,77; 4,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,1</t>
+          <t>0,12; 1,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,81</t>
+          <t>0,68; 2,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,65</t>
+          <t>0,32; 2,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,93</t>
+          <t>0,25; 2,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,28</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,09</t>
+          <t>0,31; 2,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,19</t>
+          <t>0,36; 2,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,91</t>
+          <t>1,25; 5,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,85</t>
+          <t>0,15; 0,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,17</t>
+          <t>0,69; 2,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,57</t>
+          <t>0,48; 1,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,17</t>
+          <t>1,01; 3,33</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,09</t>
+          <t>0,25; 2,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,69</t>
+          <t>0,56; 2,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,11</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,47</t>
+          <t>0,42; 2,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,16</t>
+          <t>0,45; 2,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,61</t>
+          <t>1,98; 4,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,31</t>
+          <t>0,7; 2,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,96</t>
+          <t>1,63; 3,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,73</t>
+          <t>0,55; 1,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,16</t>
+          <t>1,42; 3,14</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,48</t>
+          <t>0,47; 1,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,76</t>
+          <t>1,33; 2,89</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,23</t>
+          <t>0,8; 3,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,95</t>
+          <t>1,04; 3,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,26</t>
+          <t>0,34; 2,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,95</t>
+          <t>0,88; 3,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,31</t>
+          <t>0,97; 3,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,03</t>
+          <t>1,37; 3,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,58</t>
+          <t>0,63; 2,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,17</t>
+          <t>2,06; 4,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,88</t>
+          <t>1,03; 2,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,4</t>
+          <t>1,6; 3,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,04</t>
+          <t>0,7; 1,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,45</t>
+          <t>1,6; 3,49</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,34</t>
+          <t>1,35; 4,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,54</t>
+          <t>0,63; 3,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,32</t>
+          <t>1,62; 4,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,17</t>
+          <t>0,73; 3,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,98</t>
+          <t>1,11; 4,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,53</t>
+          <t>1,04; 4,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,18</t>
+          <t>1,28; 3,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,01</t>
+          <t>0,5; 2,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,59</t>
+          <t>1,38; 3,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,16</t>
+          <t>1,18; 3,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,26</t>
+          <t>1,69; 3,39</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,78</t>
+          <t>0,32; 3,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,95</t>
+          <t>1,57; 6,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,51</t>
+          <t>0,58; 3,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,32</t>
+          <t>1,51; 4,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,99</t>
+          <t>0,52; 2,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,11</t>
+          <t>0,27; 3,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,73</t>
+          <t>1,24; 4,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 72,78</t>
+          <t>2,44; 68,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,31</t>
+          <t>0,7; 2,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,31</t>
+          <t>1,03; 3,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,61</t>
+          <t>1,24; 3,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 57,83</t>
+          <t>2,51; 58,65</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,83</t>
+          <t>1,31; 7,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,89</t>
+          <t>1,3; 7,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,33</t>
+          <t>1,79; 5,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,59</t>
+          <t>0,97; 4,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,37</t>
+          <t>1,12; 4,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,88</t>
+          <t>1,2; 4,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,25</t>
+          <t>3,5; 6,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,34</t>
+          <t>1,49; 4,52</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,57</t>
+          <t>1,66; 4,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,11</t>
+          <t>0,94; 3,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,31</t>
+          <t>3,05; 5,28</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,28</t>
+          <t>0,61; 1,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,38</t>
+          <t>1,42; 2,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,35</t>
+          <t>0,62; 1,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,78</t>
+          <t>1,54; 2,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,59</t>
+          <t>0,84; 1,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,67</t>
+          <t>1,67; 2,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,1</t>
+          <t>1,21; 2,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,67; 25,54</t>
+          <t>2,69; 25,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,31</t>
+          <t>0,82; 1,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,35</t>
+          <t>1,63; 2,33</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,58</t>
+          <t>1,03; 1,63</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 15,07</t>
+          <t>2,35; 14,49</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>931; 8279</t>
+          <t>937; 7730</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 8262</t>
+          <t>0; 9446</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1714; 24047</t>
+          <t>1921; 27667</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5542</t>
+          <t>0; 4917</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3707; 14351</t>
+          <t>3808; 15117</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6439</t>
+          <t>0; 6364</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1167; 18246</t>
+          <t>1349; 18901</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5641</t>
+          <t>0; 4444</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5728; 17857</t>
+          <t>5716; 17606</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1086; 11600</t>
+          <t>1396; 11689</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5486; 32117</t>
+          <t>5482; 31147</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>884; 8090</t>
+          <t>881; 8777</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5027; 19325</t>
+          <t>4703; 19566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1827; 9757</t>
+          <t>1875; 12079</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1080; 12401</t>
+          <t>1078; 11386</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>956; 8017</t>
+          <t>0; 7959</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1888; 12784</t>
+          <t>1912; 13173</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1944; 12361</t>
+          <t>2005; 11630</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6501; 25160</t>
+          <t>6395; 25982</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1993; 11503</t>
+          <t>2073; 12268</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9481; 28089</t>
+          <t>8913; 25886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5687; 18174</t>
+          <t>5581; 17165</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9423; 29664</t>
+          <t>9443; 31170</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1616; 13350</t>
+          <t>1583; 13807</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3881; 18352</t>
+          <t>3787; 17547</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>891; 7430</t>
+          <t>0; 7576</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2383; 13234</t>
+          <t>2240; 13370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3096; 14898</t>
+          <t>3136; 14602</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13554; 32785</t>
+          <t>14072; 34198</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3904; 15250</t>
+          <t>4652; 16074</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9843; 23470</t>
+          <t>9665; 23145</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6828; 22922</t>
+          <t>7252; 22967</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19957; 43953</t>
+          <t>19826; 43789</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6462; 19663</t>
+          <t>6280; 19240</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14910; 31168</t>
+          <t>15052; 32662</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4137; 16792</t>
+          <t>4158; 16619</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6483; 24269</t>
+          <t>6377; 23502</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2815; 14573</t>
+          <t>2201; 14524</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7020; 35033</t>
+          <t>7787; 34571</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4904; 17055</t>
+          <t>5009; 17748</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8969; 24813</t>
+          <t>8436; 24584</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4475; 16757</t>
+          <t>4063; 16257</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14341; 29725</t>
+          <t>14706; 29008</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11504; 29757</t>
+          <t>10675; 28824</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18189; 41902</t>
+          <t>19680; 40472</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9457; 26375</t>
+          <t>9034; 25824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23392; 55281</t>
+          <t>25690; 55916</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6102</t>
+          <t>0; 6163</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5224; 18638</t>
+          <t>5784; 20982</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2997; 16922</t>
+          <t>3029; 15662</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9307; 24248</t>
+          <t>9068; 24146</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2216; 12809</t>
+          <t>2931; 14863</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4256; 17837</t>
+          <t>4983; 18411</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5535; 22488</t>
+          <t>5163; 22132</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7245; 17426</t>
+          <t>7020; 17892</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3893; 15860</t>
+          <t>3960; 16326</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13112; 31451</t>
+          <t>12105; 31361</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10780; 30849</t>
+          <t>11495; 32722</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18575; 36207</t>
+          <t>18707; 37583</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>943; 8144</t>
+          <t>935; 9168</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4761; 18437</t>
+          <t>4849; 18766</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2000; 11722</t>
+          <t>1928; 11754</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5248; 15898</t>
+          <t>5558; 15889</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1799; 10251</t>
+          <t>1794; 10041</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>977; 10998</t>
+          <t>970; 11659</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4883; 17855</t>
+          <t>4696; 17729</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15568; 442748</t>
+          <t>14868; 419562</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3712; 14709</t>
+          <t>4465; 15603</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7093; 21969</t>
+          <t>6843; 23016</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8749; 25704</t>
+          <t>8825; 24857</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24431; 564763</t>
+          <t>24538; 572784</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2570; 14345</t>
+          <t>2742; 14738</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3337; 17206</t>
+          <t>3246; 17627</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5753</t>
+          <t>0; 5006</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5194; 15065</t>
+          <t>5058; 15083</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2716; 15312</t>
+          <t>3254; 15300</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4387; 16991</t>
+          <t>4363; 17464</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4890; 19533</t>
+          <t>4819; 19539</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14242; 26618</t>
+          <t>14888; 27231</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8181; 23612</t>
+          <t>8097; 24597</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10394; 29221</t>
+          <t>10614; 28962</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6045; 20467</t>
+          <t>6184; 21556</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21488; 37593</t>
+          <t>21592; 37402</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>19763; 41995</t>
+          <t>20150; 42995</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>46068; 81624</t>
+          <t>48781; 85110</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22447; 45701</t>
+          <t>21114; 46130</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>55572; 96163</t>
+          <t>53415; 92622</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>28622; 53787</t>
+          <t>28386; 53962</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>58274; 95142</t>
+          <t>59306; 92986</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>43518; 74307</t>
+          <t>42883; 74139</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>99266; 948285</t>
+          <t>99799; 932453</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53688; 87187</t>
+          <t>54557; 87362</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>113673; 164089</t>
+          <t>114140; 162553</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70551; 109519</t>
+          <t>71741; 113052</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>166849; 1081122</t>
+          <t>168822; 1039504</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_psíq_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,7</t>
+          <t>0,21; 1,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,92</t>
+          <t>0,89; 6,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,51</t>
+          <t>0,87; 3,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 6,03</t>
+          <t>0,63; 5,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,99</t>
+          <t>0,66; 2,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,43</t>
+          <t>0,13; 1,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,37</t>
+          <t>1,24; 4,85</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,19</t>
+          <t>0,12; 1,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,85</t>
+          <t>0,71; 2,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,05</t>
+          <t>0,32; 1,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,69</t>
+          <t>0,25; 2,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,16</t>
+          <t>0,31; 2,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,06</t>
+          <t>0,35; 2,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,07</t>
+          <t>1,39; 4,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,9</t>
+          <t>0,15; 0,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,0</t>
+          <t>0,66; 2,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,49</t>
+          <t>0,46; 1,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,33</t>
+          <t>1,14; 3,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,16</t>
+          <t>0,25; 2,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,57</t>
+          <t>0,55; 2,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,13; 1,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,49</t>
+          <t>0,55; 2,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,12</t>
+          <t>0,44; 2,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,81</t>
+          <t>1,81; 4,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,43</t>
+          <t>0,58; 2,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,91</t>
+          <t>2,01; 4,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,73</t>
+          <t>0,45; 1,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,14</t>
+          <t>1,47; 3,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,45</t>
+          <t>0,43; 1,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,89</t>
+          <t>1,65; 3,2</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,2</t>
+          <t>0,79; 3,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,82</t>
+          <t>1,01; 4,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,25</t>
+          <t>0,44; 2,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,89</t>
+          <t>1,9; 4,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,44</t>
+          <t>0,95; 3,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,99</t>
+          <t>1,54; 4,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,5</t>
+          <t>0,64; 2,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,07</t>
+          <t>2,13; 4,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,79</t>
+          <t>1,13; 2,77</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,29</t>
+          <t>1,53; 3,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,99</t>
+          <t>0,67; 2,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,49</t>
+          <t>2,29; 3,89</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1277,42 +1277,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,89</t>
+          <t>1,24; 4,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,28</t>
+          <t>0,62; 3,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,3</t>
+          <t>1,51; 4,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,68</t>
+          <t>0,61; 3,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,11</t>
+          <t>1,01; 4,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,45</t>
+          <t>1,26; 4,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,27</t>
+          <t>1,35; 3,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,58</t>
+          <t>1,42; 3,51</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,36</t>
+          <t>1,08; 3,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,39</t>
+          <t>1,74; 3,25</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,13</t>
+          <t>0,32; 2,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,06</t>
+          <t>1,32; 5,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,52</t>
+          <t>0,84; 3,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,32</t>
+          <t>1,59; 4,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,93</t>
+          <t>0,52; 3,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,29</t>
+          <t>0,27; 3,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,69</t>
+          <t>1,28; 4,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 68,97</t>
+          <t>2,2; 5,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,46</t>
+          <t>0,59; 2,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,47</t>
+          <t>1,12; 3,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,49</t>
+          <t>1,27; 3,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 58,65</t>
+          <t>2,22; 4,17</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,02</t>
+          <t>1,59; 7,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,05</t>
+          <t>1,32; 6,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,33</t>
+          <t>1,73; 5,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,58</t>
+          <t>0,82; 4,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,49</t>
+          <t>1,38; 4,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,88</t>
+          <t>1,24; 4,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,39</t>
+          <t>3,31; 6,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,52</t>
+          <t>1,27; 4,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,53</t>
+          <t>1,68; 4,61</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,28</t>
+          <t>0,89; 3,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,28</t>
+          <t>3,03; 5,24</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1697,32 +1697,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,31</t>
+          <t>0,63; 1,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,48</t>
+          <t>1,41; 2,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,36</t>
+          <t>0,64; 1,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,68</t>
+          <t>1,82; 2,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,6</t>
+          <t>0,84; 1,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,61</t>
+          <t>1,65; 2,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,27 +1732,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 25,12</t>
+          <t>2,6; 3,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,31</t>
+          <t>0,79; 1,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,33</t>
+          <t>1,65; 2,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,63</t>
+          <t>1,03; 1,58</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,49</t>
+          <t>2,34; 3,07</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>11053</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>19564</t>
         </is>
       </c>
     </row>
@@ -2073,57 +2073,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>937; 7730</t>
+          <t>939; 7457</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9446</t>
+          <t>0; 8421</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1921; 27667</t>
+          <t>3637; 24516</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4917</t>
+          <t>0; 4910</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3808; 15117</t>
+          <t>3749; 15431</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6364</t>
+          <t>0; 6731</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1349; 18901</t>
+          <t>2293; 21502</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4444</t>
+          <t>0; 4909</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5716; 17606</t>
+          <t>5839; 20264</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1396; 11689</t>
+          <t>1079; 10983</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5482; 31147</t>
+          <t>9559; 37353</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>18525</t>
         </is>
       </c>
     </row>
@@ -2276,22 +2276,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>881; 8777</t>
+          <t>878; 8337</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4703; 19566</t>
+          <t>4906; 19943</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1875; 12079</t>
+          <t>1866; 10560</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1078; 11386</t>
+          <t>1190; 11937</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2301,37 +2301,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1912; 13173</t>
+          <t>1889; 14232</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2005; 11630</t>
+          <t>1949; 11529</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6395; 25982</t>
+          <t>6985; 25046</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2073; 12268</t>
+          <t>2031; 12009</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8913; 25886</t>
+          <t>8535; 26663</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5581; 17165</t>
+          <t>5343; 18084</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9443; 31170</t>
+          <t>11118; 30416</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>27995</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1583; 13807</t>
+          <t>1585; 13173</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3787; 17547</t>
+          <t>3756; 19119</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7576</t>
+          <t>898; 8296</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2240; 13370</t>
+          <t>3422; 15626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3136; 14602</t>
+          <t>3044; 13769</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14072; 34198</t>
+          <t>12835; 32502</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4652; 16074</t>
+          <t>3814; 15431</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9665; 23145</t>
+          <t>12508; 28041</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7252; 22967</t>
+          <t>6019; 22110</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19826; 43789</t>
+          <t>20470; 43881</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6280; 19240</t>
+          <t>5688; 18963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15052; 32662</t>
+          <t>20549; 39754</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>22139</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41097</t>
+          <t>42778</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4158; 16619</t>
+          <t>4098; 17449</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6377; 23502</t>
+          <t>6212; 25022</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2201; 14524</t>
+          <t>2855; 14794</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7787; 34571</t>
+          <t>13279; 32383</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5009; 17748</t>
+          <t>4880; 17303</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8436; 24584</t>
+          <t>9498; 25963</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4063; 16257</t>
+          <t>4185; 16472</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14706; 29008</t>
+          <t>15709; 31087</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10675; 28824</t>
+          <t>11720; 28692</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19680; 40472</t>
+          <t>18811; 41605</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9034; 25824</t>
+          <t>8714; 25992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25690; 55916</t>
+          <t>32851; 55914</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11602</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26563</t>
+          <t>29476</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6163</t>
+          <t>0; 6222</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5784; 20982</t>
+          <t>5311; 19263</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3029; 15662</t>
+          <t>2947; 14945</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9068; 24146</t>
+          <t>9196; 25102</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2931; 14863</t>
+          <t>2454; 13736</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4983; 18411</t>
+          <t>4518; 19236</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5163; 22132</t>
+          <t>6271; 22517</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7020; 17892</t>
+          <t>8207; 19884</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3960; 16326</t>
+          <t>3989; 16264</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12105; 31361</t>
+          <t>12447; 30796</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11495; 32722</t>
+          <t>10568; 30514</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18707; 37583</t>
+          <t>21168; 39637</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>216866</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>226640</t>
+          <t>25731</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>935; 9168</t>
+          <t>944; 8382</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4849; 18766</t>
+          <t>4090; 17890</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1928; 11754</t>
+          <t>2817; 11640</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5558; 15889</t>
+          <t>6460; 17994</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1794; 10041</t>
+          <t>1798; 10936</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>970; 11659</t>
+          <t>965; 10918</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4696; 17729</t>
+          <t>4831; 17997</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14868; 419562</t>
+          <t>9668; 22171</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4465; 15603</t>
+          <t>3747; 14571</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6843; 23016</t>
+          <t>7422; 23496</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8825; 24857</t>
+          <t>9059; 26143</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24538; 572784</t>
+          <t>18773; 35255</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>31188</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2742; 14738</t>
+          <t>3338; 15331</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3246; 17627</t>
+          <t>3297; 17440</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5006</t>
+          <t>0; 5702</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5058; 15083</t>
+          <t>5359; 16170</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3254; 15300</t>
+          <t>2737; 15501</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4363; 17464</t>
+          <t>5354; 18411</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4819; 19539</t>
+          <t>4961; 19088</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>14888; 27231</t>
+          <t>15393; 29165</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8097; 24597</t>
+          <t>6911; 22740</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10614; 28962</t>
+          <t>10741; 29472</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6184; 21556</t>
+          <t>5830; 20837</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21592; 37402</t>
+          <t>23458; 40585</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>81098</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>304229</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>377213</t>
+          <t>195258</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20150; 42995</t>
+          <t>20555; 44210</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>48781; 85110</t>
+          <t>48481; 83120</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21114; 46130</t>
+          <t>21819; 44714</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>53415; 92622</t>
+          <t>64472; 102248</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>28386; 53962</t>
+          <t>28524; 55457</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>59306; 92986</t>
+          <t>58689; 93319</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>42883; 74139</t>
+          <t>42859; 73940</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>99799; 932453</t>
+          <t>97053; 135221</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>54557; 87362</t>
+          <t>52846; 86909</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>114140; 162553</t>
+          <t>114989; 163756</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>71741; 113052</t>
+          <t>71447; 109788</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>168822; 1039504</t>
+          <t>170301; 223138</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_psíq_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
